--- a/etf_holdings/2026-09-15_00985A_full_holdings.xlsx
+++ b/etf_holdings/2026-09-15_00985A_full_holdings.xlsx
@@ -491,7 +491,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-09-15 00:02:08</t>
+          <t>2026-09-15 19:53:32</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -509,25 +509,25 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>-1.24%2380</t>
+          <t>+0.21%2385</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>-1.24%</t>
+          <t>+0.21%</t>
         </is>
       </c>
       <c r="H2" t="n">
-        <v>2380</v>
+        <v>2385</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>14.87%637,000</t>
+          <t>14.79%637,000</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>14.87%</t>
+          <t>14.79%</t>
         </is>
       </c>
       <c r="K2" t="n">
@@ -535,7 +535,7 @@
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>-0.19%</t>
+          <t>+0.03%</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">
@@ -552,7 +552,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-09-15 00:02:08</t>
+          <t>2026-09-15 19:53:32</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -570,25 +570,25 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>-0.97%612</t>
+          <t>-3.27%592</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>-0.97%</t>
+          <t>-3.27%</t>
         </is>
       </c>
       <c r="H3" t="n">
-        <v>612</v>
+        <v>592</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>4.23%706,000</t>
+          <t>4.22%706,000</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>4.23%</t>
+          <t>4.22%</t>
         </is>
       </c>
       <c r="K3" t="n">
@@ -596,7 +596,7 @@
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>-0.04%</t>
+          <t>-0.14%</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
@@ -613,7 +613,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-09-15 00:02:08</t>
+          <t>2026-09-15 19:53:32</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -631,25 +631,25 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>-1.43%344</t>
+          <t>-0.29%343</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>-1.43%</t>
+          <t>-0.29%</t>
         </is>
       </c>
       <c r="H4" t="n">
-        <v>344</v>
+        <v>343</v>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>4.11%1,215,000</t>
+          <t>4.08%1,215,000</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>4.11%</t>
+          <t>4.08%</t>
         </is>
       </c>
       <c r="K4" t="n">
@@ -657,7 +657,7 @@
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>-0.06%</t>
+          <t>-0.01%</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
@@ -674,7 +674,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-09-15 00:02:08</t>
+          <t>2026-09-15 19:53:32</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -692,7 +692,7 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>+0.47%106</t>
+          <t>+0.47%106.5</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -701,16 +701,16 @@
         </is>
       </c>
       <c r="H5" t="n">
-        <v>106</v>
+        <v>106.5</v>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>3.92%3,832,000</t>
+          <t>3.96%3,832,000</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>3.92%</t>
+          <t>3.96%</t>
         </is>
       </c>
       <c r="K5" t="n">
@@ -735,7 +735,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2026-09-15 00:02:08</t>
+          <t>2026-09-15 19:53:32</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -753,25 +753,25 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>+1.42%142.5</t>
+          <t>+0.7%143.5</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>+1.42%</t>
+          <t>+0.7%</t>
         </is>
       </c>
       <c r="H6" t="n">
-        <v>142.5</v>
+        <v>143.5</v>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>3.85%2,828,000</t>
+          <t>3.93%2,828,000</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>3.85%</t>
+          <t>3.93%</t>
         </is>
       </c>
       <c r="K6" t="n">
@@ -779,7 +779,7 @@
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>+0.05%</t>
+          <t>+0.03%</t>
         </is>
       </c>
       <c r="M6" t="inlineStr">
@@ -796,7 +796,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2026-09-15 00:02:08</t>
+          <t>2026-09-15 19:53:32</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -814,16 +814,16 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>-0.55%4560</t>
+          <t>-2.85%4430</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>-0.55%</t>
+          <t>-2.85%</t>
         </is>
       </c>
       <c r="H7" t="n">
-        <v>4560</v>
+        <v>4430</v>
       </c>
       <c r="I7" t="inlineStr">
         <is>
@@ -840,7 +840,7 @@
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>-0.02%</t>
+          <t>-0.09%</t>
         </is>
       </c>
       <c r="M7" t="inlineStr">
@@ -857,7 +857,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2026-09-15 00:02:08</t>
+          <t>2026-09-15 19:53:32</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -875,16 +875,16 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>-0.59%670</t>
+          <t>+2.24%685</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>-0.59%</t>
+          <t>+2.24%</t>
         </is>
       </c>
       <c r="H8" t="n">
-        <v>670</v>
+        <v>685</v>
       </c>
       <c r="I8" t="inlineStr">
         <is>
@@ -901,7 +901,7 @@
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>-0.02%</t>
+          <t>+0.06%</t>
         </is>
       </c>
       <c r="M8" t="inlineStr">
@@ -918,7 +918,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2026-09-15 00:02:08</t>
+          <t>2026-09-15 19:53:32</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -936,25 +936,25 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>-0.37%5345</t>
+          <t>-4.3%5115</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>-0.37%</t>
+          <t>-4.3%</t>
         </is>
       </c>
       <c r="H9" t="n">
-        <v>5345</v>
+        <v>5115</v>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>2.70%52,000</t>
+          <t>2.71%52,000</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>2.70%</t>
+          <t>2.71%</t>
         </is>
       </c>
       <c r="K9" t="n">
@@ -962,7 +962,7 @@
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>-0.01%</t>
+          <t>-0.12%</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
@@ -979,7 +979,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2026-09-15 00:02:08</t>
+          <t>2026-09-15 19:53:32</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -997,25 +997,25 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>-1.73%2270</t>
+          <t>+1.98%2315</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>-1.73%</t>
+          <t>+1.98%</t>
         </is>
       </c>
       <c r="H10" t="n">
-        <v>2270</v>
+        <v>2315</v>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>2.55%114,036</t>
+          <t>2.53%114,036</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>2.55%</t>
+          <t>2.53%</t>
         </is>
       </c>
       <c r="K10" t="n">
@@ -1023,7 +1023,7 @@
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>-0.04%</t>
+          <t>+0.05%</t>
         </is>
       </c>
       <c r="M10" t="inlineStr">
@@ -1040,7 +1040,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>2026-09-15 00:02:08</t>
+          <t>2026-09-15 19:53:32</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1058,25 +1058,25 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>+0.2%248.5</t>
+          <t>-0.8%246.5</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>+0.2%</t>
+          <t>-0.8%</t>
         </is>
       </c>
       <c r="H11" t="n">
-        <v>248.5</v>
+        <v>246.5</v>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>2.45%1,021,000</t>
+          <t>2.48%1,021,000</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>2.45%</t>
+          <t>2.48%</t>
         </is>
       </c>
       <c r="K11" t="n">
@@ -1084,7 +1084,7 @@
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>+0.00%</t>
+          <t>-0.02%</t>
         </is>
       </c>
       <c r="M11" t="inlineStr">
@@ -1101,7 +1101,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2026-09-15 00:02:08</t>
+          <t>2026-09-15 19:53:32</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1119,25 +1119,25 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>-4.79%1590</t>
+          <t>-5.03%1510</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>-4.79%</t>
+          <t>-5.03%</t>
         </is>
       </c>
       <c r="H12" t="n">
-        <v>1590</v>
+        <v>1510</v>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>2.26%140,000</t>
+          <t>2.17%140,000</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>2.26%</t>
+          <t>2.17%</t>
         </is>
       </c>
       <c r="K12" t="n">
@@ -1162,7 +1162,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>2026-09-15 00:02:08</t>
+          <t>2026-09-15 19:53:32</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -1180,25 +1180,25 @@
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>+1.15%70.3</t>
+          <t>-1.85%69</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>+1.15%</t>
+          <t>-1.85%</t>
         </is>
       </c>
       <c r="H13" t="n">
-        <v>70.3</v>
+        <v>69</v>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>1.95%2,904,000</t>
+          <t>1.99%2,904,000</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>1.95%</t>
+          <t>1.99%</t>
         </is>
       </c>
       <c r="K13" t="n">
@@ -1206,7 +1206,7 @@
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>+0.02%</t>
+          <t>-0.04%</t>
         </is>
       </c>
       <c r="M13" t="inlineStr">
@@ -1223,7 +1223,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>2026-09-15 00:02:08</t>
+          <t>2026-09-15 19:53:32</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -1241,16 +1241,16 @@
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>-0.72%970</t>
+          <t>-1.96%951</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>-0.72%</t>
+          <t>-1.96%</t>
         </is>
       </c>
       <c r="H14" t="n">
-        <v>970</v>
+        <v>951</v>
       </c>
       <c r="I14" t="inlineStr">
         <is>
@@ -1267,7 +1267,7 @@
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>-0.01%</t>
+          <t>-0.04%</t>
         </is>
       </c>
       <c r="M14" t="inlineStr">
@@ -1284,7 +1284,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>2026-09-15 00:02:08</t>
+          <t>2026-09-15 19:53:32</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -1302,25 +1302,25 @@
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>+1.01%150.5</t>
+          <t>-1.66%148</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>+1.01%</t>
+          <t>-1.66%</t>
         </is>
       </c>
       <c r="H15" t="n">
-        <v>150.5</v>
+        <v>148</v>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>1.75%1,213,000</t>
+          <t>1.78%1,213,000</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>1.75%</t>
+          <t>1.78%</t>
         </is>
       </c>
       <c r="K15" t="n">
@@ -1328,7 +1328,7 @@
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>+0.02%</t>
+          <t>-0.03%</t>
         </is>
       </c>
       <c r="M15" t="inlineStr">
@@ -1345,7 +1345,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>2026-09-15 00:02:08</t>
+          <t>2026-09-15 19:53:32</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -1358,38 +1358,38 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>2610中華航空</t>
+          <t>2891中國信託金融控股</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>-0.98%20.2</t>
+          <t>+2.35%69.7</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>-0.98%</t>
+          <t>+2.35%</t>
         </is>
       </c>
       <c r="H16" t="n">
-        <v>20.2</v>
+        <v>69.7</v>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>1.74%8,783,000</t>
+          <t>1.76%2,652,000</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>1.74%</t>
+          <t>1.76%</t>
         </is>
       </c>
       <c r="K16" t="n">
-        <v>8783000</v>
+        <v>2652000</v>
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>-0.02%</t>
+          <t>+0.04%</t>
         </is>
       </c>
       <c r="M16" t="inlineStr">
@@ -1406,7 +1406,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>2026-09-15 00:02:09</t>
+          <t>2026-09-15 19:53:34</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -1419,38 +1419,38 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>2891中國信託金融控股</t>
+          <t>2610中華航空</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>+1.49%68.1</t>
+          <t>-1.49%19.9</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>+1.49%</t>
+          <t>-1.49%</t>
         </is>
       </c>
       <c r="H17" t="n">
-        <v>68.09999999999999</v>
+        <v>19.9</v>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>1.72%2,652,000</t>
+          <t>1.73%8,783,000</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>1.72%</t>
+          <t>1.73%</t>
         </is>
       </c>
       <c r="K17" t="n">
-        <v>2652000</v>
+        <v>8783000</v>
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>+0.03%</t>
+          <t>-0.03%</t>
         </is>
       </c>
       <c r="M17" t="inlineStr">
@@ -1467,7 +1467,7 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>2026-09-15 00:02:09</t>
+          <t>2026-09-15 19:53:34</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -1480,38 +1480,38 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>6446藥華醫藥</t>
+          <t>2603長榮海運</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>-7.03%1190</t>
+          <t>-1.48%233.5</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>-7.03%</t>
+          <t>-1.48%</t>
         </is>
       </c>
       <c r="H18" t="n">
-        <v>1190</v>
+        <v>233.5</v>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>1.71%138,000</t>
+          <t>1.68%726,000</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>1.71%</t>
+          <t>1.68%</t>
         </is>
       </c>
       <c r="K18" t="n">
-        <v>138000</v>
+        <v>726000</v>
       </c>
       <c r="L18" t="inlineStr">
         <is>
-          <t>-0.13%</t>
+          <t>-0.03%</t>
         </is>
       </c>
       <c r="M18" t="inlineStr">
@@ -1528,7 +1528,7 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>2026-09-15 00:02:09</t>
+          <t>2026-09-15 19:53:34</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -1546,25 +1546,25 @@
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>-1.78%3310</t>
+          <t>-5.89%3115</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>-1.78%</t>
+          <t>-5.89%</t>
         </is>
       </c>
       <c r="H19" t="n">
-        <v>3310</v>
+        <v>3115</v>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>1.70%52,000</t>
+          <t>1.68%52,000</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>1.70%</t>
+          <t>1.68%</t>
         </is>
       </c>
       <c r="K19" t="n">
@@ -1572,7 +1572,7 @@
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>-0.03%</t>
+          <t>-0.10%</t>
         </is>
       </c>
       <c r="M19" t="inlineStr">
@@ -1589,7 +1589,7 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>2026-09-15 00:02:09</t>
+          <t>2026-09-15 19:53:34</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -1602,25 +1602,25 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>3661世芯電子</t>
+          <t>2308台達電子工業</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>-1.64%3590</t>
+          <t>+3.09%1670</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>-1.64%</t>
+          <t>+3.09%</t>
         </is>
       </c>
       <c r="H20" t="n">
-        <v>3590</v>
+        <v>1670</v>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>1.66%47,000</t>
+          <t>1.66%105,000</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
@@ -1629,11 +1629,11 @@
         </is>
       </c>
       <c r="K20" t="n">
-        <v>47000</v>
+        <v>105000</v>
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>-0.03%</t>
+          <t>+0.05%</t>
         </is>
       </c>
       <c r="M20" t="inlineStr">
@@ -1650,7 +1650,7 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>2026-09-15 00:02:09</t>
+          <t>2026-09-15 19:53:34</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -1663,25 +1663,25 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>2603長榮海運</t>
+          <t>3661世芯電子</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>+1.07%237</t>
+          <t>-6.55%3355</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>+1.07%</t>
+          <t>-6.55%</t>
         </is>
       </c>
       <c r="H21" t="n">
-        <v>237</v>
+        <v>3355</v>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>1.65%726,000</t>
+          <t>1.65%47,000</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
@@ -1690,11 +1690,11 @@
         </is>
       </c>
       <c r="K21" t="n">
-        <v>726000</v>
+        <v>47000</v>
       </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>+0.02%</t>
+          <t>-0.11%</t>
         </is>
       </c>
       <c r="M21" t="inlineStr">
@@ -1711,7 +1711,7 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>2026-09-15 00:02:09</t>
+          <t>2026-09-15 19:53:34</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -1724,38 +1724,38 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>2308台達電子工業</t>
+          <t>6446藥華醫藥</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>0%1620</t>
+          <t>+1.26%1205</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>+1.26%</t>
         </is>
       </c>
       <c r="H22" t="n">
-        <v>1620</v>
+        <v>1205</v>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>1.65%105,000</t>
+          <t>1.60%138,000</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>1.65%</t>
+          <t>1.60%</t>
         </is>
       </c>
       <c r="K22" t="n">
-        <v>105000</v>
+        <v>138000</v>
       </c>
       <c r="L22" t="inlineStr">
         <is>
-          <t>+0.00%</t>
+          <t>+0.02%</t>
         </is>
       </c>
       <c r="M22" t="inlineStr">
@@ -1772,7 +1772,7 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>2026-09-15 00:02:09</t>
+          <t>2026-09-15 19:53:34</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -1790,25 +1790,25 @@
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>+0.18%545</t>
+          <t>-1.47%537</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>+0.18%</t>
+          <t>-1.47%</t>
         </is>
       </c>
       <c r="H23" t="n">
-        <v>545</v>
+        <v>537</v>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>1.55%295,000</t>
+          <t>1.57%295,000</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>1.55%</t>
+          <t>1.57%</t>
         </is>
       </c>
       <c r="K23" t="n">
@@ -1816,7 +1816,7 @@
       </c>
       <c r="L23" t="inlineStr">
         <is>
-          <t>+0.00%</t>
+          <t>-0.02%</t>
         </is>
       </c>
       <c r="M23" t="inlineStr">
@@ -1833,7 +1833,7 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>2026-09-15 00:02:09</t>
+          <t>2026-09-15 19:53:34</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -1851,25 +1851,25 @@
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>-1.75%1960</t>
+          <t>-3.57%1890</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>-1.75%</t>
+          <t>-3.57%</t>
         </is>
       </c>
       <c r="H24" t="n">
-        <v>1960</v>
+        <v>1890</v>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>1.55%80,000</t>
+          <t>1.53%80,000</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>1.55%</t>
+          <t>1.53%</t>
         </is>
       </c>
       <c r="K24" t="n">
@@ -1877,7 +1877,7 @@
       </c>
       <c r="L24" t="inlineStr">
         <is>
-          <t>-0.03%</t>
+          <t>-0.06%</t>
         </is>
       </c>
       <c r="M24" t="inlineStr">
@@ -1894,7 +1894,7 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>2026-09-15 00:02:09</t>
+          <t>2026-09-15 19:53:34</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -1907,38 +1907,38 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>3491昇達科技</t>
+          <t>2881富邦金融控股</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>+4.43%1415</t>
+          <t>-1.95%151</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>+4.43%</t>
+          <t>-1.95%</t>
         </is>
       </c>
       <c r="H25" t="n">
-        <v>1415</v>
+        <v>151</v>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>1.47%107,000</t>
+          <t>1.51%1,004,000</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>1.47%</t>
+          <t>1.51%</t>
         </is>
       </c>
       <c r="K25" t="n">
-        <v>107000</v>
+        <v>1004000</v>
       </c>
       <c r="L25" t="inlineStr">
         <is>
-          <t>+0.06%</t>
+          <t>-0.03%</t>
         </is>
       </c>
       <c r="M25" t="inlineStr">
@@ -1955,7 +1955,7 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>2026-09-15 00:02:09</t>
+          <t>2026-09-15 19:53:34</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -1973,16 +1973,16 @@
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>-0.53%1875</t>
+          <t>-1.87%1840</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>-0.53%</t>
+          <t>-1.87%</t>
         </is>
       </c>
       <c r="H26" t="n">
-        <v>1875</v>
+        <v>1840</v>
       </c>
       <c r="I26" t="inlineStr">
         <is>
@@ -1999,7 +1999,7 @@
       </c>
       <c r="L26" t="inlineStr">
         <is>
-          <t>-0.01%</t>
+          <t>-0.03%</t>
         </is>
       </c>
       <c r="M26" t="inlineStr">
@@ -2016,7 +2016,7 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>2026-09-15 00:02:09</t>
+          <t>2026-09-15 19:53:34</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -2029,38 +2029,38 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>2881富邦金融控股</t>
+          <t>3491昇達科技</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>+3.7%154</t>
+          <t>-2.52%1355</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>+3.7%</t>
+          <t>-2.52%</t>
         </is>
       </c>
       <c r="H27" t="n">
-        <v>154</v>
+        <v>1355</v>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>1.44%1,004,000</t>
+          <t>1.45%107,000</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>1.44%</t>
+          <t>1.45%</t>
         </is>
       </c>
       <c r="K27" t="n">
-        <v>1004000</v>
+        <v>107000</v>
       </c>
       <c r="L27" t="inlineStr">
         <is>
-          <t>+0.05%</t>
+          <t>-0.04%</t>
         </is>
       </c>
       <c r="M27" t="inlineStr">
@@ -2077,7 +2077,7 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>2026-09-15 00:02:09</t>
+          <t>2026-09-15 19:53:34</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -2095,25 +2095,25 @@
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>+4.27%1955</t>
+          <t>+1.28%1980</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>+4.27%</t>
+          <t>+1.28%</t>
         </is>
       </c>
       <c r="H28" t="n">
-        <v>1955</v>
+        <v>1980</v>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>1.34%74,000</t>
+          <t>1.41%74,000</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>1.34%</t>
+          <t>1.41%</t>
         </is>
       </c>
       <c r="K28" t="n">
@@ -2121,7 +2121,7 @@
       </c>
       <c r="L28" t="inlineStr">
         <is>
-          <t>+0.05%</t>
+          <t>+0.02%</t>
         </is>
       </c>
       <c r="M28" t="inlineStr">
@@ -2138,7 +2138,7 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>2026-09-15 00:02:09</t>
+          <t>2026-09-15 19:53:34</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -2156,25 +2156,25 @@
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>-1.64%902</t>
+          <t>+1.56%914</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>-1.64%</t>
+          <t>+1.56%</t>
         </is>
       </c>
       <c r="H29" t="n">
-        <v>902</v>
+        <v>914</v>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>1.25%143,000</t>
+          <t>1.26%143,000</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>1.25%</t>
+          <t>1.26%</t>
         </is>
       </c>
       <c r="K29" t="n">
@@ -2182,7 +2182,7 @@
       </c>
       <c r="L29" t="inlineStr">
         <is>
-          <t>-0.02%</t>
+          <t>+0.02%</t>
         </is>
       </c>
       <c r="M29" t="inlineStr">
@@ -2199,7 +2199,7 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>2026-09-15 00:02:09</t>
+          <t>2026-09-15 19:53:34</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -2217,25 +2217,25 @@
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>-0.53%74.6</t>
+          <t>-0.13%74.5</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>-0.53%</t>
+          <t>-0.13%</t>
         </is>
       </c>
       <c r="H30" t="n">
-        <v>74.59999999999999</v>
+        <v>74.5</v>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>1.20%1,657,000</t>
+          <t>1.21%1,657,000</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>1.20%</t>
+          <t>1.21%</t>
         </is>
       </c>
       <c r="K30" t="n">
@@ -2243,7 +2243,7 @@
       </c>
       <c r="L30" t="inlineStr">
         <is>
-          <t>-0.01%</t>
+          <t>-0.00%</t>
         </is>
       </c>
       <c r="M30" t="inlineStr">
@@ -2260,7 +2260,7 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>2026-09-15 00:02:09</t>
+          <t>2026-09-15 19:53:34</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -2278,25 +2278,25 @@
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>-0.08%6305</t>
+          <t>-2.7%6135</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>-0.08%</t>
+          <t>-2.7%</t>
         </is>
       </c>
       <c r="H31" t="n">
-        <v>6305</v>
+        <v>6135</v>
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>1.10%18,000</t>
+          <t>1.11%18,000</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>1.10%</t>
+          <t>1.11%</t>
         </is>
       </c>
       <c r="K31" t="n">
@@ -2304,7 +2304,7 @@
       </c>
       <c r="L31" t="inlineStr">
         <is>
-          <t>-0.00%</t>
+          <t>-0.03%</t>
         </is>
       </c>
       <c r="M31" t="inlineStr">
@@ -2321,7 +2321,7 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>2026-09-15 00:02:11</t>
+          <t>2026-09-15 19:53:36</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -2334,34 +2334,34 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>8046南亞電路板</t>
+          <t>2303聯華電子</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>-2.31%1055</t>
+          <t>-2.81%138.5</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>-2.31%</t>
+          <t>-2.81%</t>
         </is>
       </c>
       <c r="H32" t="n">
-        <v>1055</v>
+        <v>138.5</v>
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>1.07%102,000</t>
+          <t>1.06%766,000</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>1.07%</t>
+          <t>1.06%</t>
         </is>
       </c>
       <c r="K32" t="n">
-        <v>102000</v>
+        <v>766000</v>
       </c>
       <c r="L32" t="inlineStr">
         <is>
@@ -2382,7 +2382,7 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>2026-09-15 00:02:11</t>
+          <t>2026-09-15 19:53:36</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -2395,38 +2395,38 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>2303聯華電子</t>
+          <t>8046南亞電路板</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>+1.42%142.5</t>
+          <t>+2.84%1085</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>+1.42%</t>
+          <t>+2.84%</t>
         </is>
       </c>
       <c r="H33" t="n">
-        <v>142.5</v>
+        <v>1085</v>
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>1.04%766,000</t>
+          <t>1.05%102,000</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
         <is>
-          <t>1.04%</t>
+          <t>1.05%</t>
         </is>
       </c>
       <c r="K33" t="n">
-        <v>766000</v>
+        <v>102000</v>
       </c>
       <c r="L33" t="inlineStr">
         <is>
-          <t>+0.01%</t>
+          <t>+0.03%</t>
         </is>
       </c>
       <c r="M33" t="inlineStr">
@@ -2443,7 +2443,7 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>2026-09-15 00:02:11</t>
+          <t>2026-09-15 19:53:36</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -2456,38 +2456,38 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>8996高力熱處理工業</t>
+          <t>2027大成不銹鋼工業</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>-7.14%1235</t>
+          <t>-1.64%45</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>-7.14%</t>
+          <t>-1.64%</t>
         </is>
       </c>
       <c r="H34" t="n">
-        <v>1235</v>
+        <v>45</v>
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>0.98%76,000</t>
+          <t>0.94%2,097,000</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
         <is>
-          <t>0.98%</t>
+          <t>0.94%</t>
         </is>
       </c>
       <c r="K34" t="n">
-        <v>76000</v>
+        <v>2097000</v>
       </c>
       <c r="L34" t="inlineStr">
         <is>
-          <t>-0.07%</t>
+          <t>-0.02%</t>
         </is>
       </c>
       <c r="M34" t="inlineStr">
@@ -2504,7 +2504,7 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>2026-09-15 00:02:11</t>
+          <t>2026-09-15 19:53:36</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -2517,38 +2517,38 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>2027大成不銹鋼工業</t>
+          <t>8996高力熱處理工業</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>-1.61%45.75</t>
+          <t>-1.21%1220</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>-1.61%</t>
+          <t>-1.21%</t>
         </is>
       </c>
       <c r="H35" t="n">
-        <v>45.75</v>
+        <v>1220</v>
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>0.94%2,097,000</t>
+          <t>0.92%76,000</t>
         </is>
       </c>
       <c r="J35" t="inlineStr">
         <is>
-          <t>0.94%</t>
+          <t>0.92%</t>
         </is>
       </c>
       <c r="K35" t="n">
-        <v>2097000</v>
+        <v>76000</v>
       </c>
       <c r="L35" t="inlineStr">
         <is>
-          <t>-0.02%</t>
+          <t>-0.01%</t>
         </is>
       </c>
       <c r="M35" t="inlineStr">
@@ -2565,7 +2565,7 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>2026-09-15 00:02:11</t>
+          <t>2026-09-15 19:53:36</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -2583,16 +2583,16 @@
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>-0.93%2140</t>
+          <t>-2.8%2080</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>-0.93%</t>
+          <t>-2.8%</t>
         </is>
       </c>
       <c r="H36" t="n">
-        <v>2140</v>
+        <v>2080</v>
       </c>
       <c r="I36" t="inlineStr">
         <is>
@@ -2609,7 +2609,7 @@
       </c>
       <c r="L36" t="inlineStr">
         <is>
-          <t>-0.01%</t>
+          <t>-0.03%</t>
         </is>
       </c>
       <c r="M36" t="inlineStr">
@@ -2626,7 +2626,7 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>2026-09-15 00:02:11</t>
+          <t>2026-09-15 19:53:36</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -2644,25 +2644,25 @@
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>+0.95%5820</t>
+          <t>-8.76%5310</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>+0.95%</t>
+          <t>-8.76%</t>
         </is>
       </c>
       <c r="H37" t="n">
-        <v>5820</v>
+        <v>5310</v>
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>0.73%13,000</t>
+          <t>0.74%13,000</t>
         </is>
       </c>
       <c r="J37" t="inlineStr">
         <is>
-          <t>0.73%</t>
+          <t>0.74%</t>
         </is>
       </c>
       <c r="K37" t="n">
@@ -2670,7 +2670,7 @@
       </c>
       <c r="L37" t="inlineStr">
         <is>
-          <t>+0.01%</t>
+          <t>-0.07%</t>
         </is>
       </c>
       <c r="M37" t="inlineStr">
@@ -2687,7 +2687,7 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>2026-09-15 00:02:11</t>
+          <t>2026-09-15 19:53:36</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -2700,38 +2700,38 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>6187萬潤科技</t>
+          <t>6147頎邦科技</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>-2.34%1250</t>
+          <t>+5.82%200</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>-2.34%</t>
+          <t>+5.82%</t>
         </is>
       </c>
       <c r="H38" t="n">
-        <v>1250</v>
+        <v>200</v>
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>0.73%60,000</t>
+          <t>0.72%390,000</t>
         </is>
       </c>
       <c r="J38" t="inlineStr">
         <is>
-          <t>0.73%</t>
+          <t>0.72%</t>
         </is>
       </c>
       <c r="K38" t="n">
-        <v>60000</v>
+        <v>390000</v>
       </c>
       <c r="L38" t="inlineStr">
         <is>
-          <t>-0.02%</t>
+          <t>+0.04%</t>
         </is>
       </c>
       <c r="M38" t="inlineStr">
@@ -2748,7 +2748,7 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>2026-09-15 00:02:11</t>
+          <t>2026-09-15 19:53:36</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -2761,38 +2761,38 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>1301台灣塑膠工業</t>
+          <t>6187萬潤科技</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>-2.63%62.9</t>
+          <t>-0.82%1215</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>-2.63%</t>
+          <t>-0.82%</t>
         </is>
       </c>
       <c r="H39" t="n">
-        <v>62.9</v>
+        <v>1215</v>
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>0.69%1,103,000</t>
+          <t>0.72%60,000</t>
         </is>
       </c>
       <c r="J39" t="inlineStr">
         <is>
-          <t>0.69%</t>
+          <t>0.72%</t>
         </is>
       </c>
       <c r="K39" t="n">
-        <v>1103000</v>
+        <v>60000</v>
       </c>
       <c r="L39" t="inlineStr">
         <is>
-          <t>-0.02%</t>
+          <t>-0.01%</t>
         </is>
       </c>
       <c r="M39" t="inlineStr">
@@ -2809,7 +2809,7 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>2026-09-15 00:02:11</t>
+          <t>2026-09-15 19:53:36</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -2822,25 +2822,25 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>6147頎邦科技</t>
+          <t>1301台灣塑膠工業</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>-4.99%181</t>
+          <t>-1.43%62</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>-4.99%</t>
+          <t>-1.43%</t>
         </is>
       </c>
       <c r="H40" t="n">
-        <v>181</v>
+        <v>62</v>
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>0.68%390,000</t>
+          <t>0.68%1,103,000</t>
         </is>
       </c>
       <c r="J40" t="inlineStr">
@@ -2849,11 +2849,11 @@
         </is>
       </c>
       <c r="K40" t="n">
-        <v>390000</v>
+        <v>1103000</v>
       </c>
       <c r="L40" t="inlineStr">
         <is>
-          <t>-0.04%</t>
+          <t>-0.01%</t>
         </is>
       </c>
       <c r="M40" t="inlineStr">
@@ -2870,7 +2870,7 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>2026-09-15 00:02:11</t>
+          <t>2026-09-15 19:53:36</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
@@ -2888,16 +2888,16 @@
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>-0.71%2810</t>
+          <t>-2.55%2675</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>-0.71%</t>
+          <t>-2.55%</t>
         </is>
       </c>
       <c r="H41" t="n">
-        <v>2810</v>
+        <v>2675</v>
       </c>
       <c r="I41" t="inlineStr">
         <is>
@@ -2914,7 +2914,7 @@
       </c>
       <c r="L41" t="inlineStr">
         <is>
-          <t>-0.00%</t>
+          <t>-0.01%</t>
         </is>
       </c>
       <c r="M41" t="inlineStr">
@@ -2931,7 +2931,7 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>2026-09-15 00:02:11</t>
+          <t>2026-09-15 19:53:36</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
@@ -2949,25 +2949,25 @@
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>-6.71%160</t>
+          <t>-0.31%159.5</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>-6.71%</t>
+          <t>-0.31%</t>
         </is>
       </c>
       <c r="H42" t="n">
-        <v>160</v>
+        <v>159.5</v>
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>0.40%243,000</t>
+          <t>0.38%243,000</t>
         </is>
       </c>
       <c r="J42" t="inlineStr">
         <is>
-          <t>0.40%</t>
+          <t>0.38%</t>
         </is>
       </c>
       <c r="K42" t="n">
@@ -2975,7 +2975,7 @@
       </c>
       <c r="L42" t="inlineStr">
         <is>
-          <t>-0.03%</t>
+          <t>-0.00%</t>
         </is>
       </c>
       <c r="M42" t="inlineStr">
@@ -2992,7 +2992,7 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>2026-09-15 00:02:11</t>
+          <t>2026-09-15 19:53:36</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
@@ -3010,25 +3010,25 @@
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>-4.06%473</t>
+          <t>-1.59%465.5</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>-4.06%</t>
+          <t>-1.59%</t>
         </is>
       </c>
       <c r="H43" t="n">
-        <v>473</v>
+        <v>465.5</v>
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>0.38%79,000</t>
+          <t>0.36%79,000</t>
         </is>
       </c>
       <c r="J43" t="inlineStr">
         <is>
-          <t>0.38%</t>
+          <t>0.36%</t>
         </is>
       </c>
       <c r="K43" t="n">
@@ -3036,7 +3036,7 @@
       </c>
       <c r="L43" t="inlineStr">
         <is>
-          <t>-0.02%</t>
+          <t>-0.01%</t>
         </is>
       </c>
       <c r="M43" t="inlineStr">
@@ -3053,7 +3053,7 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>2026-09-15 00:02:11</t>
+          <t>2026-09-15 19:53:36</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
@@ -3071,16 +3071,16 @@
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>-5.49%2325</t>
+          <t>+0.43%2320</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>-5.49%</t>
+          <t>+0.43%</t>
         </is>
       </c>
       <c r="H44" t="n">
-        <v>2325</v>
+        <v>2320</v>
       </c>
       <c r="I44" t="inlineStr">
         <is>
@@ -3097,7 +3097,7 @@
       </c>
       <c r="L44" t="inlineStr">
         <is>
-          <t>-0.02%</t>
+          <t>+0.00%</t>
         </is>
       </c>
       <c r="M44" t="inlineStr">
@@ -3114,7 +3114,7 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>2026-09-15 00:02:11</t>
+          <t>2026-09-15 19:53:36</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
@@ -3132,16 +3132,16 @@
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>-0.75%11990</t>
+          <t>-2.29%11715</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>-0.75%</t>
+          <t>-2.29%</t>
         </is>
       </c>
       <c r="H45" t="n">
-        <v>11990</v>
+        <v>11715</v>
       </c>
       <c r="I45" t="inlineStr">
         <is>
@@ -3175,7 +3175,7 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>2026-09-15 00:02:11</t>
+          <t>2026-09-15 19:53:36</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
@@ -3193,16 +3193,16 @@
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>-9.98%5995</t>
+          <t>+1%6055</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>-9.98%</t>
+          <t>+1%</t>
         </is>
       </c>
       <c r="H46" t="n">
-        <v>5995</v>
+        <v>6055</v>
       </c>
       <c r="I46" t="inlineStr">
         <is>
@@ -3219,7 +3219,7 @@
       </c>
       <c r="L46" t="inlineStr">
         <is>
-          <t>-0.01%</t>
+          <t>+0.00%</t>
         </is>
       </c>
       <c r="M46" t="inlineStr">
@@ -3236,7 +3236,7 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>2026-09-15 00:02:12</t>
+          <t>2026-09-15 19:53:37</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
@@ -3254,16 +3254,16 @@
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>-3.63%1990</t>
+          <t>-0.78%1920</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>-3.63%</t>
+          <t>-0.78%</t>
         </is>
       </c>
       <c r="H47" t="n">
-        <v>1990</v>
+        <v>1920</v>
       </c>
       <c r="I47" t="inlineStr">
         <is>
@@ -3297,7 +3297,7 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>2026-09-15 00:02:12</t>
+          <t>2026-09-15 19:53:37</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
@@ -3315,16 +3315,16 @@
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>-2.92%798</t>
+          <t>-0.38%795</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>-2.92%</t>
+          <t>-0.38%</t>
         </is>
       </c>
       <c r="H48" t="n">
-        <v>798</v>
+        <v>795</v>
       </c>
       <c r="I48" t="inlineStr">
         <is>
@@ -3358,7 +3358,7 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>2026-09-15 00:02:12</t>
+          <t>2026-09-15 19:53:37</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
@@ -3376,16 +3376,16 @@
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>-5.2%437.5</t>
+          <t>+2.25%454</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>-5.2%</t>
+          <t>+2.25%</t>
         </is>
       </c>
       <c r="H49" t="n">
-        <v>437.5</v>
+        <v>454</v>
       </c>
       <c r="I49" t="inlineStr">
         <is>
@@ -3402,7 +3402,7 @@
       </c>
       <c r="L49" t="inlineStr">
         <is>
-          <t>-0.00%</t>
+          <t>+0.00%</t>
         </is>
       </c>
       <c r="M49" t="inlineStr">
@@ -3419,7 +3419,7 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>2026-09-15 00:02:12</t>
+          <t>2026-09-15 19:53:37</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
@@ -3437,16 +3437,16 @@
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>-0.97%1020</t>
+          <t>-4.71%972</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>-0.97%</t>
+          <t>-4.71%</t>
         </is>
       </c>
       <c r="H50" t="n">
-        <v>1020</v>
+        <v>972</v>
       </c>
       <c r="I50" t="inlineStr">
         <is>
@@ -3480,7 +3480,7 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>2026-09-15 00:02:12</t>
+          <t>2026-09-15 19:53:37</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
@@ -3498,16 +3498,16 @@
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>+0.52%192</t>
+          <t>+0.26%192.5</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>+0.52%</t>
+          <t>+0.26%</t>
         </is>
       </c>
       <c r="H51" t="n">
-        <v>192</v>
+        <v>192.5</v>
       </c>
       <c r="I51" t="inlineStr">
         <is>

--- a/etf_holdings/2026-09-15_00985A_full_holdings.xlsx
+++ b/etf_holdings/2026-09-15_00985A_full_holdings.xlsx
@@ -491,7 +491,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-09-15 19:53:32</t>
+          <t>2026-09-15 21:12:32</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -552,7 +552,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-09-15 19:53:32</t>
+          <t>2026-09-15 21:12:32</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -613,7 +613,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-09-15 19:53:32</t>
+          <t>2026-09-15 21:12:32</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -674,7 +674,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-09-15 19:53:32</t>
+          <t>2026-09-15 21:12:32</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -735,7 +735,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2026-09-15 19:53:32</t>
+          <t>2026-09-15 21:12:32</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -796,7 +796,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2026-09-15 19:53:32</t>
+          <t>2026-09-15 21:12:32</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -857,7 +857,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2026-09-15 19:53:32</t>
+          <t>2026-09-15 21:12:32</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -918,7 +918,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2026-09-15 19:53:32</t>
+          <t>2026-09-15 21:12:32</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -979,7 +979,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2026-09-15 19:53:32</t>
+          <t>2026-09-15 21:12:32</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -1040,7 +1040,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>2026-09-15 19:53:32</t>
+          <t>2026-09-15 21:12:32</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1101,7 +1101,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2026-09-15 19:53:32</t>
+          <t>2026-09-15 21:12:32</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1162,7 +1162,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>2026-09-15 19:53:32</t>
+          <t>2026-09-15 21:12:32</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -1223,7 +1223,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>2026-09-15 19:53:32</t>
+          <t>2026-09-15 21:12:32</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -1284,7 +1284,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>2026-09-15 19:53:32</t>
+          <t>2026-09-15 21:12:32</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -1345,7 +1345,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>2026-09-15 19:53:32</t>
+          <t>2026-09-15 21:12:32</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -1406,7 +1406,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>2026-09-15 19:53:34</t>
+          <t>2026-09-15 21:12:33</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -1467,7 +1467,7 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>2026-09-15 19:53:34</t>
+          <t>2026-09-15 21:12:33</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -1528,7 +1528,7 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>2026-09-15 19:53:34</t>
+          <t>2026-09-15 21:12:33</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -1589,7 +1589,7 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>2026-09-15 19:53:34</t>
+          <t>2026-09-15 21:12:33</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -1650,7 +1650,7 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>2026-09-15 19:53:34</t>
+          <t>2026-09-15 21:12:33</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -1711,7 +1711,7 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>2026-09-15 19:53:34</t>
+          <t>2026-09-15 21:12:33</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -1772,7 +1772,7 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>2026-09-15 19:53:34</t>
+          <t>2026-09-15 21:12:33</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -1833,7 +1833,7 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>2026-09-15 19:53:34</t>
+          <t>2026-09-15 21:12:33</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -1894,7 +1894,7 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>2026-09-15 19:53:34</t>
+          <t>2026-09-15 21:12:33</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -1955,7 +1955,7 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>2026-09-15 19:53:34</t>
+          <t>2026-09-15 21:12:33</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -2016,7 +2016,7 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>2026-09-15 19:53:34</t>
+          <t>2026-09-15 21:12:33</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -2077,7 +2077,7 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>2026-09-15 19:53:34</t>
+          <t>2026-09-15 21:12:33</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -2138,7 +2138,7 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>2026-09-15 19:53:34</t>
+          <t>2026-09-15 21:12:33</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -2199,7 +2199,7 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>2026-09-15 19:53:34</t>
+          <t>2026-09-15 21:12:33</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -2260,7 +2260,7 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>2026-09-15 19:53:34</t>
+          <t>2026-09-15 21:12:33</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -2321,7 +2321,7 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>2026-09-15 19:53:36</t>
+          <t>2026-09-15 21:12:34</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -2382,7 +2382,7 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>2026-09-15 19:53:36</t>
+          <t>2026-09-15 21:12:34</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -2443,7 +2443,7 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>2026-09-15 19:53:36</t>
+          <t>2026-09-15 21:12:34</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -2504,7 +2504,7 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>2026-09-15 19:53:36</t>
+          <t>2026-09-15 21:12:34</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -2565,7 +2565,7 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>2026-09-15 19:53:36</t>
+          <t>2026-09-15 21:12:34</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -2626,7 +2626,7 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>2026-09-15 19:53:36</t>
+          <t>2026-09-15 21:12:34</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -2687,7 +2687,7 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>2026-09-15 19:53:36</t>
+          <t>2026-09-15 21:12:34</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -2748,7 +2748,7 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>2026-09-15 19:53:36</t>
+          <t>2026-09-15 21:12:34</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -2809,7 +2809,7 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>2026-09-15 19:53:36</t>
+          <t>2026-09-15 21:12:34</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -2870,7 +2870,7 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>2026-09-15 19:53:36</t>
+          <t>2026-09-15 21:12:34</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
@@ -2931,7 +2931,7 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>2026-09-15 19:53:36</t>
+          <t>2026-09-15 21:12:34</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
@@ -2992,7 +2992,7 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>2026-09-15 19:53:36</t>
+          <t>2026-09-15 21:12:34</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
@@ -3053,7 +3053,7 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>2026-09-15 19:53:36</t>
+          <t>2026-09-15 21:12:34</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
@@ -3114,7 +3114,7 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>2026-09-15 19:53:36</t>
+          <t>2026-09-15 21:12:34</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
@@ -3175,7 +3175,7 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>2026-09-15 19:53:36</t>
+          <t>2026-09-15 21:12:34</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
@@ -3236,7 +3236,7 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>2026-09-15 19:53:37</t>
+          <t>2026-09-15 21:12:35</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
@@ -3297,7 +3297,7 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>2026-09-15 19:53:37</t>
+          <t>2026-09-15 21:12:35</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
@@ -3358,7 +3358,7 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>2026-09-15 19:53:37</t>
+          <t>2026-09-15 21:12:35</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
@@ -3419,7 +3419,7 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>2026-09-15 19:53:37</t>
+          <t>2026-09-15 21:12:35</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
@@ -3480,7 +3480,7 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>2026-09-15 19:53:37</t>
+          <t>2026-09-15 21:12:35</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">

--- a/etf_holdings/2026-09-15_00985A_full_holdings.xlsx
+++ b/etf_holdings/2026-09-15_00985A_full_holdings.xlsx
@@ -491,7 +491,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-09-15 21:12:32</t>
+          <t>2026-09-15 22:22:47</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -552,7 +552,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-09-15 21:12:32</t>
+          <t>2026-09-15 22:22:47</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -613,7 +613,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-09-15 21:12:32</t>
+          <t>2026-09-15 22:22:47</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -674,7 +674,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-09-15 21:12:32</t>
+          <t>2026-09-15 22:22:47</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -735,7 +735,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2026-09-15 21:12:32</t>
+          <t>2026-09-15 22:22:47</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -796,7 +796,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2026-09-15 21:12:32</t>
+          <t>2026-09-15 22:22:47</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -857,7 +857,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2026-09-15 21:12:32</t>
+          <t>2026-09-15 22:22:47</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -918,7 +918,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2026-09-15 21:12:32</t>
+          <t>2026-09-15 22:22:47</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -979,7 +979,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2026-09-15 21:12:32</t>
+          <t>2026-09-15 22:22:47</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -1040,7 +1040,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>2026-09-15 21:12:32</t>
+          <t>2026-09-15 22:22:47</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1101,7 +1101,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2026-09-15 21:12:32</t>
+          <t>2026-09-15 22:22:47</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1162,7 +1162,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>2026-09-15 21:12:32</t>
+          <t>2026-09-15 22:22:47</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -1223,7 +1223,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>2026-09-15 21:12:32</t>
+          <t>2026-09-15 22:22:47</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -1284,7 +1284,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>2026-09-15 21:12:32</t>
+          <t>2026-09-15 22:22:47</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -1345,7 +1345,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>2026-09-15 21:12:32</t>
+          <t>2026-09-15 22:22:47</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -1406,7 +1406,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>2026-09-15 21:12:33</t>
+          <t>2026-09-15 22:22:48</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -1467,7 +1467,7 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>2026-09-15 21:12:33</t>
+          <t>2026-09-15 22:22:48</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -1528,7 +1528,7 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>2026-09-15 21:12:33</t>
+          <t>2026-09-15 22:22:48</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -1589,7 +1589,7 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>2026-09-15 21:12:33</t>
+          <t>2026-09-15 22:22:48</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -1650,7 +1650,7 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>2026-09-15 21:12:33</t>
+          <t>2026-09-15 22:22:48</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -1711,7 +1711,7 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>2026-09-15 21:12:33</t>
+          <t>2026-09-15 22:22:48</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -1772,7 +1772,7 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>2026-09-15 21:12:33</t>
+          <t>2026-09-15 22:22:48</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -1833,7 +1833,7 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>2026-09-15 21:12:33</t>
+          <t>2026-09-15 22:22:48</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -1894,7 +1894,7 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>2026-09-15 21:12:33</t>
+          <t>2026-09-15 22:22:48</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -1955,7 +1955,7 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>2026-09-15 21:12:33</t>
+          <t>2026-09-15 22:22:48</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -2016,7 +2016,7 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>2026-09-15 21:12:33</t>
+          <t>2026-09-15 22:22:48</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -2077,7 +2077,7 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>2026-09-15 21:12:33</t>
+          <t>2026-09-15 22:22:48</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -2138,7 +2138,7 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>2026-09-15 21:12:33</t>
+          <t>2026-09-15 22:22:48</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -2199,7 +2199,7 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>2026-09-15 21:12:33</t>
+          <t>2026-09-15 22:22:48</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -2260,7 +2260,7 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>2026-09-15 21:12:33</t>
+          <t>2026-09-15 22:22:48</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -2321,7 +2321,7 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>2026-09-15 21:12:34</t>
+          <t>2026-09-15 22:22:50</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -2382,7 +2382,7 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>2026-09-15 21:12:34</t>
+          <t>2026-09-15 22:22:50</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -2443,7 +2443,7 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>2026-09-15 21:12:34</t>
+          <t>2026-09-15 22:22:50</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -2504,7 +2504,7 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>2026-09-15 21:12:34</t>
+          <t>2026-09-15 22:22:50</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -2565,7 +2565,7 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>2026-09-15 21:12:34</t>
+          <t>2026-09-15 22:22:50</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -2626,7 +2626,7 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>2026-09-15 21:12:34</t>
+          <t>2026-09-15 22:22:50</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -2687,7 +2687,7 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>2026-09-15 21:12:34</t>
+          <t>2026-09-15 22:22:50</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -2748,7 +2748,7 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>2026-09-15 21:12:34</t>
+          <t>2026-09-15 22:22:50</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -2809,7 +2809,7 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>2026-09-15 21:12:34</t>
+          <t>2026-09-15 22:22:50</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -2870,7 +2870,7 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>2026-09-15 21:12:34</t>
+          <t>2026-09-15 22:22:50</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
@@ -2931,7 +2931,7 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>2026-09-15 21:12:34</t>
+          <t>2026-09-15 22:22:50</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
@@ -2992,7 +2992,7 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>2026-09-15 21:12:34</t>
+          <t>2026-09-15 22:22:50</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
@@ -3053,7 +3053,7 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>2026-09-15 21:12:34</t>
+          <t>2026-09-15 22:22:50</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
@@ -3114,7 +3114,7 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>2026-09-15 21:12:34</t>
+          <t>2026-09-15 22:22:50</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
@@ -3175,7 +3175,7 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>2026-09-15 21:12:34</t>
+          <t>2026-09-15 22:22:50</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
@@ -3236,7 +3236,7 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>2026-09-15 21:12:35</t>
+          <t>2026-09-15 22:22:51</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
@@ -3297,7 +3297,7 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>2026-09-15 21:12:35</t>
+          <t>2026-09-15 22:22:51</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
@@ -3358,7 +3358,7 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>2026-09-15 21:12:35</t>
+          <t>2026-09-15 22:22:51</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
@@ -3419,7 +3419,7 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>2026-09-15 21:12:35</t>
+          <t>2026-09-15 22:22:51</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
@@ -3480,7 +3480,7 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>2026-09-15 21:12:35</t>
+          <t>2026-09-15 22:22:51</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">

--- a/etf_holdings/2026-09-15_00985A_full_holdings.xlsx
+++ b/etf_holdings/2026-09-15_00985A_full_holdings.xlsx
@@ -491,7 +491,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-09-15 22:22:47</t>
+          <t>2026-09-15 22:28:42</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -552,7 +552,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-09-15 22:22:47</t>
+          <t>2026-09-15 22:28:42</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -613,7 +613,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-09-15 22:22:47</t>
+          <t>2026-09-15 22:28:42</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -674,7 +674,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-09-15 22:22:47</t>
+          <t>2026-09-15 22:28:42</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -735,7 +735,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2026-09-15 22:22:47</t>
+          <t>2026-09-15 22:28:42</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -796,7 +796,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2026-09-15 22:22:47</t>
+          <t>2026-09-15 22:28:42</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -857,7 +857,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2026-09-15 22:22:47</t>
+          <t>2026-09-15 22:28:42</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -918,7 +918,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2026-09-15 22:22:47</t>
+          <t>2026-09-15 22:28:42</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -979,7 +979,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2026-09-15 22:22:47</t>
+          <t>2026-09-15 22:28:42</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -1040,7 +1040,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>2026-09-15 22:22:47</t>
+          <t>2026-09-15 22:28:42</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1101,7 +1101,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2026-09-15 22:22:47</t>
+          <t>2026-09-15 22:28:42</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1162,7 +1162,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>2026-09-15 22:22:47</t>
+          <t>2026-09-15 22:28:42</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -1223,7 +1223,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>2026-09-15 22:22:47</t>
+          <t>2026-09-15 22:28:42</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -1284,7 +1284,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>2026-09-15 22:22:47</t>
+          <t>2026-09-15 22:28:42</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -1345,7 +1345,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>2026-09-15 22:22:47</t>
+          <t>2026-09-15 22:28:42</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -1406,7 +1406,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>2026-09-15 22:22:48</t>
+          <t>2026-09-15 22:28:43</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -1467,7 +1467,7 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>2026-09-15 22:22:48</t>
+          <t>2026-09-15 22:28:43</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -1528,7 +1528,7 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>2026-09-15 22:22:48</t>
+          <t>2026-09-15 22:28:43</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -1589,7 +1589,7 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>2026-09-15 22:22:48</t>
+          <t>2026-09-15 22:28:43</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -1650,7 +1650,7 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>2026-09-15 22:22:48</t>
+          <t>2026-09-15 22:28:43</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -1711,7 +1711,7 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>2026-09-15 22:22:48</t>
+          <t>2026-09-15 22:28:43</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -1772,7 +1772,7 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>2026-09-15 22:22:48</t>
+          <t>2026-09-15 22:28:43</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -1833,7 +1833,7 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>2026-09-15 22:22:48</t>
+          <t>2026-09-15 22:28:43</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -1894,7 +1894,7 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>2026-09-15 22:22:48</t>
+          <t>2026-09-15 22:28:43</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -1955,7 +1955,7 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>2026-09-15 22:22:48</t>
+          <t>2026-09-15 22:28:43</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -2016,7 +2016,7 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>2026-09-15 22:22:48</t>
+          <t>2026-09-15 22:28:43</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -2077,7 +2077,7 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>2026-09-15 22:22:48</t>
+          <t>2026-09-15 22:28:43</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -2138,7 +2138,7 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>2026-09-15 22:22:48</t>
+          <t>2026-09-15 22:28:43</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -2199,7 +2199,7 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>2026-09-15 22:22:48</t>
+          <t>2026-09-15 22:28:43</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -2260,7 +2260,7 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>2026-09-15 22:22:48</t>
+          <t>2026-09-15 22:28:43</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -2321,7 +2321,7 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>2026-09-15 22:22:50</t>
+          <t>2026-09-15 22:28:44</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -2382,7 +2382,7 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>2026-09-15 22:22:50</t>
+          <t>2026-09-15 22:28:44</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -2443,7 +2443,7 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>2026-09-15 22:22:50</t>
+          <t>2026-09-15 22:28:44</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -2504,7 +2504,7 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>2026-09-15 22:22:50</t>
+          <t>2026-09-15 22:28:44</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -2565,7 +2565,7 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>2026-09-15 22:22:50</t>
+          <t>2026-09-15 22:28:44</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -2626,7 +2626,7 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>2026-09-15 22:22:50</t>
+          <t>2026-09-15 22:28:44</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -2687,7 +2687,7 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>2026-09-15 22:22:50</t>
+          <t>2026-09-15 22:28:44</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -2748,7 +2748,7 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>2026-09-15 22:22:50</t>
+          <t>2026-09-15 22:28:44</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -2809,7 +2809,7 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>2026-09-15 22:22:50</t>
+          <t>2026-09-15 22:28:44</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -2870,7 +2870,7 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>2026-09-15 22:22:50</t>
+          <t>2026-09-15 22:28:44</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
@@ -2931,7 +2931,7 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>2026-09-15 22:22:50</t>
+          <t>2026-09-15 22:28:44</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
@@ -2992,7 +2992,7 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>2026-09-15 22:22:50</t>
+          <t>2026-09-15 22:28:44</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
@@ -3053,7 +3053,7 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>2026-09-15 22:22:50</t>
+          <t>2026-09-15 22:28:44</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
@@ -3114,7 +3114,7 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>2026-09-15 22:22:50</t>
+          <t>2026-09-15 22:28:44</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
@@ -3175,7 +3175,7 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>2026-09-15 22:22:50</t>
+          <t>2026-09-15 22:28:44</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
@@ -3236,7 +3236,7 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>2026-09-15 22:22:51</t>
+          <t>2026-09-15 22:28:45</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
@@ -3297,7 +3297,7 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>2026-09-15 22:22:51</t>
+          <t>2026-09-15 22:28:45</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
@@ -3358,7 +3358,7 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>2026-09-15 22:22:51</t>
+          <t>2026-09-15 22:28:45</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
@@ -3419,7 +3419,7 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>2026-09-15 22:22:51</t>
+          <t>2026-09-15 22:28:45</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
@@ -3480,7 +3480,7 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>2026-09-15 22:22:51</t>
+          <t>2026-09-15 22:28:45</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
